--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_344_Hong_Kong_China.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_344_Hong_Kong_China.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R1454e50816034378"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R6426174819b542ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Re3673abbc47940fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R05b4127a9d704b2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rbe3b97098ef9431f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Redb1f506854f474e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R2ab3cebfcae7431a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R6891f028b4ba4772"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R015f7151a5684443"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R83dc153f72fb491f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R77db5181f68b40b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R80b1aba159794f71"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ344CommercialTable" displayName="EEZ344CommercialTable" ref="A1:O7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O7"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ344CommercialTable" displayName="EEZ344CommercialTable" ref="A1:E7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E7"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ344FunctionalTable" displayName="EEZ344FunctionalTable" ref="A1:O16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O16"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ344FunctionalTable" displayName="EEZ344FunctionalTable" ref="A1:E16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E16"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ344ValidationTable" displayName="EEZ344ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ344ValidationTable" displayName="EEZ344ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -3977,7 +3931,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6da0c7e48f94ef3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50a90010317a4734"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3987,20 +3941,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4008,390 +3952,136 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>310.9007150389</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.3277415434879165</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>212.68729286738224</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>310.9007150389</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>224.01431827377255</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$50,A2,'Species'!$U$2:$U$50))</x:f>
-        <x:v>69646.2117302676</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.3277415434879165</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>212.68729286738224</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>66124.63143215707</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>3521.580298110537</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0532567096683727</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.05325670966837265</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2971.2363340574</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.309795606625928</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>204.0777261219704</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2971.2363340574</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>261.5924530209845</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$50,A3,'Species'!$U$2:$U$50))</x:f>
-        <x:v>777253.0011311527</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.309795606625928</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>204.0777261219704</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>606363.1548254135</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>170889.84630573925</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.2818275565489174</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.2818275565489175</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>97.8283896186</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.214717926140729</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>163.9524557643989</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>97.8283896186</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>238.18407092922553</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$50,A4,'Species'!$U$2:$U$50))</x:f>
-        <x:v>23301.164091808532</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.214717926140729</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>163.9524557643989</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>16039.204721445898</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>7261.959370362634</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.452763057550648</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.452763057550648</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>177.0478079177</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>177.0478079177</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$50,A5,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2228.899844900451</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>2228.899844900451</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>6177.0721718104005</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.311628894470085</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>204.94102051552477</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>6177.0721718104005</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>261.5376391712133</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$50,A6,'Species'!$U$2:$U$50))</x:f>
-        <x:v>1615536.8728054916</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.311628894470085</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>204.94102051552477</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1265935.4746888725</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>349601.3981166191</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.2761605193207342</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.27616051932073415</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>3726.7655119782</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.6263088578121145</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>422.96931100400866</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>3726.7655119782</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>686.2145436875966</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$50,A7,'Species'!$U$2:$U$50))</x:f>
-        <x:v>2557360.6952327928</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.6263088578121145</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>422.96931100400866</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1576307.4408749207</x:v>
       </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>981053.2543578721</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.62237430904554</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.6223743090455399</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G7">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O7">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b21906274e04099"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd12012a660674123"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4401,20 +4091,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4422,876 +4102,307 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>151.0851541371</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.748918722212159</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>560.9429862767544</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>151.0851541371</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>599.5744274085234</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$50,A2,'Species'!$U$2:$U$50))</x:f>
-        <x:v>90586.79478168023</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.748918722212159</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>560.9429862767544</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>84750.1575437486</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>5836.637237931631</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0688687479420758</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.06886874794207573</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>520.5045491512</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.330860910036133</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2142.20441498289</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>520.5045491512</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2449.908875502521</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$50,A3,'Species'!$U$2:$U$50))</x:f>
-        <x:v>1275188.714704963</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.330860910036133</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2142.20441498289</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1115027.1432103792</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>160161.57149458374</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1436391683106901</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.1436391683106902</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>233.13639275440002</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.253155711206011</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1791.2479699220362</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>233.13639275440002</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1974.8282199652197</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$50,A4,'Species'!$U$2:$U$50))</x:f>
-        <x:v>460404.3275122841</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.253155711206011</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1791.2479699220362</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>417605.09023626556</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>42799.23727601854</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1024873457644022</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.10248734576440222</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>40.4100983382</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.35</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2238.7211385683377</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>40.4100983382</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$50,A5,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>90466.9413613536</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.35</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>90466.9413613536</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>28.936373997</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1000</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>28.936373997</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>999.9999999999999</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$50,A6,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>28936.373997</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>28936.373997</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1227.0370979256998</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.4722074357080976</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>296.6247845004062</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1227.0370979256998</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>390.40033007387774</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$50,A7,'Species'!$U$2:$U$50))</x:f>
-        <x:v>479035.6880430862</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.4722074357080976</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>296.6247845004062</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>363969.6147462145</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>115066.07329687173</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.316141976239154</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.3161419762391539</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>231.27062620150002</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6912290718923697</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>491.166877505864</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>231.27062620150002</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>502.30763550069116</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$50,A8,'Species'!$U$2:$U$50))</x:f>
-        <x:v>116169.00140803966</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6912290718923697</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>491.166877505864</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>113592.47133021663</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2576.5300778230303</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0226822257465724</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.02268222574657243</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>5807.4655879683005</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.2762417497600826</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>188.90425908956803</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>5807.4655879683005</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>192.43828438165605</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$50,A9,'Species'!$U$2:$U$50))</x:f>
-        <x:v>1117578.714354125</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.2762417497600826</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>188.90425908956803</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1097054.9840833144</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>20523.730270810658</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.018708023361254</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.01870802336125389</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>195.9580844144</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.808355768847063</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>643.2144151137569</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>195.9580844144</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1060.9757072187583</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$50,A10,'Species'!$U$2:$U$50))</x:f>
-        <x:v>207906.76719680117</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.808355768847063</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>643.2144151137569</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>126043.06465342049</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>81863.70254338068</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.6494899403507888</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.6494899403507888</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1887.3690582858003</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.3451616028635773</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>221.3918364995593</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1887.3690582858003</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>239.42013064113465</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$50,A11,'Species'!$U$2:$U$50))</x:f>
-        <x:v>451874.1465028216</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.3451616028635773</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>221.3918364995593</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>417848.1019663371</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>34026.04453648446</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0814316120531897</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.08143161205318981</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>181.85985197979997</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.1087423243164505</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>12.845242996054557</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>181.85985197979997</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>12.969037297589095</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$50,A12,'Species'!$U$2:$U$50))</x:f>
-        <x:v>2358.547203260058</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.1087423243164505</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>12.845242996054557</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>2336.033989907044</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>22.513213353013725</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0096373654879522</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.009637365487952328</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1744.1992361317</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.195539542698412</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>156.8698721867965</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1744.1992361317</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>170.9766332368403</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$50,A13,'Species'!$U$2:$U$50))</x:f>
-        <x:v>298217.3130880667</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.195539542698412</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>156.8698721867965</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>273612.31124028785</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>24605.001847778854</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0899265158656206</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.08992651586562056</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>57.028600343099995</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.620204023040369</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>417.0652665482081</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>57.028600343099995</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>417.06749260360345</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$50,A14,'Species'!$U$2:$U$50))</x:f>
-        <x:v>23784.775351789714</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.620204023040369</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>417.0652665482081</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>23784.64840296623</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0.12694882348296233</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0000053374269542</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.000005337426954233651</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>811.0612555452001</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.590453240450048</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>389.45137405697096</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>811.0612555452001</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>400.6808116933629</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$50,A15,'Species'!$U$2:$U$50))</x:f>
-        <x:v>324976.6822048888</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.590453240450048</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>389.45137405697096</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>315868.92041645024</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>9107.76178843854</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0288339915697644</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.0288339915697645</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>343.5289632478</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.3346046237708085</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>216.07505079727957</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>343.5289632478</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>226.5953251519685</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$50,A16,'Species'!$U$2:$U$50))</x:f>
-        <x:v>77842.05712625387</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.3346046237708085</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>216.07505079727957</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>74228.03818410517</x:v>
       </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>3614.018942148701</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0486880568389128</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.04868805683891279</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G16">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O16">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd6d249a80d24bb9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9fc29b8e6d04ca2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5466,7 +4577,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -5565,7 +4676,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>5045326.844836414</x:v>
+        <x:v>3532998.8063877104</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5579,7 +4690,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>5045326.844836414</x:v>
+        <x:v>4545123.895361967</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5593,7 +4704,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>9.313225746154785e-10</x:v>
+        <x:v>-1512328.0384487025</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5607,7 +4718,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>9.313225746154785e-10</x:v>
+        <x:v>-500202.94947444554</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5618,9 +4729,9 @@
         <x:v>EEZ_344</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -5632,47 +4743,19 @@
         <x:v>EEZ_344</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_344</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_344</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd7b8aab2c9a4b05"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re72473f9e13446a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5719,7 +4802,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
